--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484579_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484579_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5949</v>
+        <v>10.4941</v>
       </c>
       <c r="E2" t="n">
-        <v>8.754099999999999</v>
+        <v>8.232200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8408</v>
+        <v>2.2619</v>
       </c>
       <c r="G2" t="n">
         <v>6.5901</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7378</v>
+        <v>0.6371</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5656</v>
+        <v>0.0438</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1722</v>
+        <v>0.5933</v>
       </c>
       <c r="V2" t="n">
         <v>2.5339</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3494</v>
+        <v>5.3253</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5944</v>
+        <v>2.3225</v>
       </c>
       <c r="F3" t="n">
-        <v>2.755</v>
+        <v>3.0028</v>
       </c>
       <c r="G3" t="n">
         <v>5.1082</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1644</v>
+        <v>0.8115</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7715</v>
+        <v>-0.0433</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6071</v>
+        <v>0.8548</v>
       </c>
       <c r="V3" t="n">
         <v>0.3219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1704</v>
+        <v>3.9128</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7483</v>
+        <v>2.243</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4221</v>
+        <v>1.6698</v>
       </c>
       <c r="G4" t="n">
         <v>2.7014</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2745</v>
+        <v>0.4679</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6063</v>
+        <v>-0.1116</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3318</v>
+        <v>0.5795</v>
       </c>
       <c r="V4" t="n">
         <v>0.0104</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4141</v>
+        <v>2.0976</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2966</v>
+        <v>-0.2416</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7108</v>
+        <v>2.3392</v>
       </c>
       <c r="G5" t="n">
         <v>0.1582</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3842</v>
+        <v>1.0677</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1086</v>
+        <v>0.1637</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2756</v>
+        <v>0.904</v>
       </c>
       <c r="V5" t="n">
         <v>0.3219</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9808</v>
+        <v>1.9456</v>
       </c>
       <c r="E6" t="n">
-        <v>1.835</v>
+        <v>1.6016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1458</v>
+        <v>0.344</v>
       </c>
       <c r="G6" t="n">
         <v>1.1715</v>
@@ -922,13 +922,13 @@
         <v>0.1833</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6261</v>
+        <v>0.5909</v>
       </c>
       <c r="T6" t="n">
-        <v>0.494</v>
+        <v>0.2606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1321</v>
+        <v>0.3303</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2742</v>
+        <v>0.5957</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.5256</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1366</v>
+        <v>1.1213</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6612</v>
+        <v>-0.3898</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9625</v>
+        <v>-0.5562</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3013</v>
+        <v>0.1664</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0818</v>
+        <v>0.5844</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5077</v>
+        <v>0.4177</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5895</v>
+        <v>0.1667</v>
       </c>
       <c r="M7" t="n">
-        <v>0.743</v>
+        <v>-0.9742</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4548</v>
+        <v>-0.9739</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2882</v>
+        <v>-0.0003</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7489</v>
+        <v>0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3069</v>
+        <v>0.619</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5626</v>
+        <v>-0.1938</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7443</v>
+        <v>0.8128</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>S. HATHOUTI LAHRECH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5218</v>
+        <v>0.0015</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.773</v>
+        <v>0.1373</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2948</v>
+        <v>-0.1358</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3898</v>
+        <v>-0.1771</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5562</v>
+        <v>-0.3053</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1664</v>
+        <v>0.1282</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5844</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4177</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9742</v>
+        <v>-0.1771</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9739</v>
+        <v>-0.3053</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0003</v>
+        <v>0.1282</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.545</v>
+        <v>0.1785</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4412</v>
+        <v>0.1373</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9862</v>
+        <v>0.0413</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HATHOUTI LAHRECH</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2156</v>
+        <v>-0.5591</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0551</v>
+        <v>-0.9664</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1606</v>
+        <v>0.4073</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1771</v>
+        <v>-1.0653</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3053</v>
+        <v>2.624</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1282</v>
+        <v>-3.6893</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.3492</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.731</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1771</v>
+        <v>-0.7161</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3053</v>
+        <v>-0.1069</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1282</v>
+        <v>-0.6092</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0385</v>
+        <v>0.3388</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0551</v>
+        <v>-0.0516</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0165</v>
+        <v>0.3904</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1762</v>
+        <v>-0.6681</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9586</v>
+        <v>-1.3266</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7824</v>
+        <v>0.6585</v>
       </c>
       <c r="G10" t="n">
         <v>0.8709</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3035</v>
+        <v>0.8116</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534</v>
+        <v>-0.1214</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0569</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5339</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3178</v>
+        <v>-1.1447</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5022</v>
+        <v>-2.5381</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1844</v>
+        <v>1.3934</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0653</v>
+        <v>0.6612</v>
       </c>
       <c r="H11" t="n">
-        <v>2.624</v>
+        <v>0.9625</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.6893</v>
+        <v>-0.3013</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3492</v>
+        <v>-0.0818</v>
       </c>
       <c r="K11" t="n">
-        <v>2.731</v>
+        <v>0.5077</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.0801</v>
+        <v>-0.5895</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7161</v>
+        <v>0.743</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1069</v>
+        <v>0.4548</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6092</v>
+        <v>0.2882</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0995</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.42</v>
+        <v>1.888</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5875</v>
+        <v>0.8869</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1675</v>
+        <v>1.0011</v>
       </c>
       <c r="V11" t="n">
-        <v>1.267</v>
+        <v>-0.945</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9718</v>
+        <v>-1.7299</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7225</v>
+        <v>-1.5302</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2493</v>
+        <v>-0.1998</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1066</v>
@@ -1390,13 +1390,13 @@
         <v>0.1833</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1321</v>
+        <v>0.1097</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1652</v>
+        <v>0.0272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.033</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.6242</v>
+        <v>20.2708</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7614</v>
+        <v>7.408100000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>12.8628</v>
+        <v>12.8626</v>
       </c>
       <c r="G13" t="n">
         <v>14.5227</v>
@@ -1447,7 +1447,7 @@
         <v>15.997</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3182999999999998</v>
+        <v>-0.3182999999999995</v>
       </c>
       <c r="M13" t="n">
         <v>-1.156</v>
@@ -1468,19 +1468,19 @@
         <v>10.9955</v>
       </c>
       <c r="S13" t="n">
-        <v>6.874</v>
+        <v>7.5207</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3506000000000008</v>
+        <v>0.9978</v>
       </c>
       <c r="U13" t="n">
-        <v>6.523200000000001</v>
+        <v>6.5231</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9762</v>
+        <v>0.9761999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>4.475999999999999</v>
+        <v>4.476</v>
       </c>
       <c r="X13" t="n">
         <v>-3.4997</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0404</v>
+        <v>1.0214</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3766</v>
+        <v>0.4727</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.5487</v>
       </c>
       <c r="G14" t="n">
         <v>1.6087</v>
@@ -1546,13 +1546,13 @@
         <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.118</v>
+        <v>-0.1371</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9359</v>
+        <v>-0.8397</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8178</v>
+        <v>0.7027</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6335</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0393</v>
+        <v>0.6958</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4489</v>
+        <v>2.2628</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5904</v>
+        <v>-1.567</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9293</v>
+        <v>0.4913</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2689</v>
+        <v>-1.929</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6604</v>
+        <v>2.4203</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8071</v>
+        <v>2.943</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7556</v>
+        <v>0.266</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0515</v>
+        <v>2.677</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8778</v>
+        <v>-2.4517</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4867</v>
+        <v>-2.195</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6089</v>
+        <v>-0.2567</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5419</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6576</v>
+        <v>-0.6802</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1157</v>
+        <v>0.602</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3011</v>
+        <v>-0.6335</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3011</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1768</v>
+        <v>0.474</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8782</v>
+        <v>-0.2241</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.055</v>
+        <v>0.6982</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4913</v>
+        <v>0.9293</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.929</v>
+        <v>0.2689</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4203</v>
+        <v>0.6604</v>
       </c>
       <c r="J17" t="n">
-        <v>2.943</v>
+        <v>1.8071</v>
       </c>
       <c r="K17" t="n">
-        <v>0.266</v>
+        <v>1.7556</v>
       </c>
       <c r="L17" t="n">
-        <v>2.677</v>
+        <v>0.0515</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4517</v>
+        <v>-0.8778</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.195</v>
+        <v>-1.4867</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2567</v>
+        <v>0.6089</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9163</v>
+        <v>-0.733</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9509</v>
+        <v>-0.0234</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0648</v>
+        <v>-0.0154</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1139</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6335</v>
+        <v>0.3011</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6335</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6069</v>
+        <v>-0.3869</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6498</v>
+        <v>-0.5537</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0429</v>
+        <v>0.1668</v>
       </c>
       <c r="G18" t="n">
         <v>-2.16</v>
@@ -1858,13 +1858,13 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4574</v>
+        <v>-1.2374</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.101</v>
+        <v>-1.0049</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3563</v>
+        <v>-0.2325</v>
       </c>
       <c r="V18" t="n">
         <v>1.9109</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8034</v>
+        <v>-0.4042</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8452</v>
+        <v>-1.6529</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0418</v>
+        <v>1.2487</v>
       </c>
       <c r="G19" t="n">
         <v>-0.229</v>
@@ -1936,13 +1936,13 @@
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.352</v>
+        <v>-0.9529</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6425</v>
+        <v>-0.4502</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7095</v>
+        <v>-0.5027</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6966</v>
+        <v>-1.1663</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0997</v>
+        <v>-3.0036</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4031</v>
+        <v>1.8373</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9311</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.463</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2662</v>
+        <v>-1.17</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2728</v>
+        <v>0.707</v>
       </c>
       <c r="V20" t="n">
         <v>0.945</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3334</v>
+        <v>-1.5204</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0798</v>
+        <v>0.2087</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2536</v>
+        <v>-1.7291</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8293</v>
@@ -2092,13 +2092,13 @@
         <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1664</v>
+        <v>-0.3533</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9728</v>
+        <v>-0.6844</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1935</v>
+        <v>0.3311</v>
       </c>
       <c r="V21" t="n">
         <v>0.945</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.582</v>
+        <v>-3.9143</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0716</v>
+        <v>-2.2639</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5105</v>
+        <v>-1.6504</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0123</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>0.781</v>
+        <v>0.4487</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.552</v>
+        <v>-0.7443</v>
       </c>
       <c r="U23" t="n">
-        <v>1.333</v>
+        <v>1.193</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6335</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4655</v>
+        <v>-4.1493</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4591</v>
+        <v>-4.6514</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0064</v>
+        <v>0.5021</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1809</v>
@@ -2326,13 +2326,13 @@
         <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7794</v>
+        <v>-0.4632</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0384</v>
+        <v>-0.2307</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.741</v>
+        <v>-0.2325</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7999</v>
+        <v>-5.4706</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9898</v>
+        <v>-3.0859</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8101</v>
+        <v>-2.3846</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1459</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5544</v>
+        <v>-0.2251</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1666</v>
+        <v>-0.2628</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3878</v>
+        <v>0.0377</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.624</v>
+        <v>-17.06</v>
       </c>
       <c r="E26" t="n">
         <v>-12.8626</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.7615</v>
+        <v>-4.1972</v>
       </c>
       <c r="G26" t="n">
         <v>-14.5226</v>
@@ -2470,7 +2470,7 @@
         <v>-15.9971</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3182000000000003</v>
+        <v>0.3182</v>
       </c>
       <c r="P26" t="n">
         <v>2.748799999999999</v>
@@ -2482,13 +2482,13 @@
         <v>13.7444</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.874100000000001</v>
+        <v>-4.31</v>
       </c>
       <c r="T26" t="n">
         <v>-6.523099999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3509000000000003</v>
+        <v>2.2133</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9762999999999997</v>
